--- a/artfynd/A 47417-2023 artfynd.xlsx
+++ b/artfynd/A 47417-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 47417-2023 artfynd.xlsx
+++ b/artfynd/A 47417-2023 artfynd.xlsx
@@ -7427,11 +7427,11 @@
         <v>113136412</v>
       </c>
       <c r="B58" t="n">
-        <v>90774</v>
+        <v>91168</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">

--- a/artfynd/A 47417-2023 artfynd.xlsx
+++ b/artfynd/A 47417-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY120"/>
+  <dimension ref="A1:AY122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15028,6 +15028,237 @@
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>113136184</v>
+      </c>
+      <c r="B121" t="n">
+        <v>5173</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Marieberg, Kniva, Falun, Dlr</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>544878</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6713967</v>
+      </c>
+      <c r="S121" t="n">
+        <v>25</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF121" t="inlineStr"/>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>113135312</v>
+      </c>
+      <c r="B122" t="n">
+        <v>4770</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Marieberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>544701</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6713844</v>
+      </c>
+      <c r="S122" t="n">
+        <v>25</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47417-2023 artfynd.xlsx
+++ b/artfynd/A 47417-2023 artfynd.xlsx
@@ -7427,7 +7427,7 @@
         <v>113136412</v>
       </c>
       <c r="B58" t="n">
-        <v>91168</v>
+        <v>91182</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>

--- a/artfynd/A 47417-2023 artfynd.xlsx
+++ b/artfynd/A 47417-2023 artfynd.xlsx
@@ -7427,7 +7427,7 @@
         <v>113136412</v>
       </c>
       <c r="B58" t="n">
-        <v>91182</v>
+        <v>91184</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>

--- a/artfynd/A 47417-2023 artfynd.xlsx
+++ b/artfynd/A 47417-2023 artfynd.xlsx
@@ -7427,7 +7427,7 @@
         <v>113136412</v>
       </c>
       <c r="B58" t="n">
-        <v>91184</v>
+        <v>91185</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>

--- a/artfynd/A 47417-2023 artfynd.xlsx
+++ b/artfynd/A 47417-2023 artfynd.xlsx
@@ -7427,7 +7427,7 @@
         <v>113136412</v>
       </c>
       <c r="B58" t="n">
-        <v>91185</v>
+        <v>91194</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -15030,10 +15030,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>113136184</v>
+        <v>113135312</v>
       </c>
       <c r="B121" t="n">
-        <v>5173</v>
+        <v>4770</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -15046,39 +15046,35 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Marieberg, Kniva, Falun, Dlr</t>
+          <t>Marieberg, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>544878</v>
+        <v>544701</v>
       </c>
       <c r="R121" t="n">
-        <v>6713967</v>
+        <v>6713844</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -15110,7 +15106,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -15120,7 +15116,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -15129,7 +15125,6 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -15148,10 +15143,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>113135312</v>
+        <v>113136184</v>
       </c>
       <c r="B122" t="n">
-        <v>4770</v>
+        <v>5173</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -15164,35 +15159,39 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100299</v>
+        <v>100526</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Marieberg, Dlr</t>
+          <t>Marieberg, Kniva, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>544701</v>
+        <v>544878</v>
       </c>
       <c r="R122" t="n">
-        <v>6713844</v>
+        <v>6713967</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -15224,7 +15223,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -15234,7 +15233,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15243,6 +15242,7 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 47417-2023 artfynd.xlsx
+++ b/artfynd/A 47417-2023 artfynd.xlsx
@@ -15030,10 +15030,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>113135312</v>
+        <v>113136184</v>
       </c>
       <c r="B121" t="n">
-        <v>4770</v>
+        <v>5173</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -15046,35 +15046,39 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100299</v>
+        <v>100526</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Marieberg, Dlr</t>
+          <t>Marieberg, Kniva, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>544701</v>
+        <v>544878</v>
       </c>
       <c r="R121" t="n">
-        <v>6713844</v>
+        <v>6713967</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -15106,7 +15110,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -15116,7 +15120,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -15125,6 +15129,7 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -15143,10 +15148,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>113136184</v>
+        <v>113135312</v>
       </c>
       <c r="B122" t="n">
-        <v>5173</v>
+        <v>4770</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -15159,39 +15164,35 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Marieberg, Kniva, Falun, Dlr</t>
+          <t>Marieberg, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>544878</v>
+        <v>544701</v>
       </c>
       <c r="R122" t="n">
-        <v>6713967</v>
+        <v>6713844</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -15223,7 +15224,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -15233,7 +15234,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15242,7 +15243,6 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 47417-2023 artfynd.xlsx
+++ b/artfynd/A 47417-2023 artfynd.xlsx
@@ -15030,10 +15030,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>113136184</v>
+        <v>113135312</v>
       </c>
       <c r="B121" t="n">
-        <v>5173</v>
+        <v>4770</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -15046,39 +15046,35 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Marieberg, Kniva, Falun, Dlr</t>
+          <t>Marieberg, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>544878</v>
+        <v>544701</v>
       </c>
       <c r="R121" t="n">
-        <v>6713967</v>
+        <v>6713844</v>
       </c>
       <c r="S121" t="n">
         <v>25</v>
@@ -15110,7 +15106,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -15120,7 +15116,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -15129,7 +15125,6 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -15148,10 +15143,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>113135312</v>
+        <v>113136184</v>
       </c>
       <c r="B122" t="n">
-        <v>4770</v>
+        <v>5173</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -15164,35 +15159,39 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100299</v>
+        <v>100526</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Marieberg, Dlr</t>
+          <t>Marieberg, Kniva, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>544701</v>
+        <v>544878</v>
       </c>
       <c r="R122" t="n">
-        <v>6713844</v>
+        <v>6713967</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -15224,7 +15223,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -15234,7 +15233,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15243,6 +15242,7 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 47417-2023 artfynd.xlsx
+++ b/artfynd/A 47417-2023 artfynd.xlsx
@@ -15123,7 +15123,7 @@
         <v>0</v>
       </c>
       <c r="AE121" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG121" t="b">
         <v>0</v>

--- a/artfynd/A 47417-2023 artfynd.xlsx
+++ b/artfynd/A 47417-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY135"/>
+  <dimension ref="A1:AZ135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113136038</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -905,6 +915,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113135135</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1016,6 +1031,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97118848</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1124,6 +1144,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110561329</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1235,6 +1260,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113063917</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1343,6 +1373,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113175798</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1459,6 +1494,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113122126</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1572,6 +1612,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113228940</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1689,6 +1734,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113134657</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1804,6 +1854,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113121791</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1912,6 +1967,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113135312</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2025,6 +2085,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96887016</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2142,6 +2207,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98292382</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2250,6 +2320,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110561890</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2363,6 +2438,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113135056</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2471,6 +2551,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113135456</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2584,6 +2669,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113136184</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2692,6 +2782,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113136300</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2810,6 +2905,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113136325</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2928,6 +3028,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113135643</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3045,6 +3150,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98292491</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3167,6 +3277,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98292565</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3289,6 +3404,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98292875</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3402,6 +3522,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113121866</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3519,6 +3644,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113122072</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3632,6 +3762,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113135228</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3759,6 +3894,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102963911</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3884,6 +4024,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119144764</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4007,6 +4152,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87181634</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4123,6 +4273,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126660825</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4247,6 +4402,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113120760</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4368,6 +4528,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113121281</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4484,6 +4649,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113121354</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4605,6 +4775,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113122167</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4734,6 +4909,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113136469</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4842,6 +5022,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113220063</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4959,6 +5144,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96886705</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5067,6 +5257,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110561717</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5175,6 +5370,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97116680</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5283,6 +5483,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97118903</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5391,6 +5596,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97119173</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5499,6 +5709,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97119195</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5607,6 +5822,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97119548</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5723,6 +5943,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113228860</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5840,6 +6065,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113120487</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5948,6 +6178,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113218100</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6059,6 +6294,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113120386</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6170,6 +6410,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113136412</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6278,6 +6523,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113119860</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6386,6 +6636,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113219151</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6497,6 +6752,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113231717</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6621,6 +6881,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113095571</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6738,6 +7003,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113095609</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6846,6 +7116,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113218728</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6962,6 +7237,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59914</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7070,6 +7350,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113097329</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7178,6 +7463,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113100756</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7286,6 +7576,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113100899</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7394,6 +7689,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113122504</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7502,6 +7802,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113137483</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7615,6 +7920,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113219439</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7728,6 +8038,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113099095</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7843,6 +8158,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113220064</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7956,6 +8276,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113100458</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8064,6 +8389,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113116333</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8177,6 +8507,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113219216</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8305,6 +8640,11 @@
       <c r="AY68" t="inlineStr">
         <is>
           <t>Falu kommun inventering ansvarsarter</t>
+        </is>
+      </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59912</t>
         </is>
       </c>
     </row>
@@ -8424,6 +8764,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113101459</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8532,6 +8877,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113116385</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8640,6 +8990,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113116445</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8764,6 +9119,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113119255</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8885,6 +9245,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113119569</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9007,6 +9372,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113119911</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9128,6 +9498,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113120170</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9245,6 +9620,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113120175</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9366,6 +9746,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113120522</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9482,6 +9867,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113120574</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9599,6 +9989,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113120689</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9720,6 +10115,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113120719</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9832,6 +10232,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113122647</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9958,6 +10363,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113122915</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -10066,6 +10476,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113136791</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10192,6 +10607,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113137272</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10318,6 +10738,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113137463</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10444,6 +10869,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113137932</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10552,6 +10982,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113218014</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10660,6 +11095,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113218049</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10768,6 +11208,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113218050</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10893,6 +11338,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113218125</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -11001,6 +11451,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113218134</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -11113,6 +11568,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113218252</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -11221,6 +11681,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113218270</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11350,6 +11815,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113218283</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11475,6 +11945,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113218341</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11583,6 +12058,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113218342</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11691,6 +12171,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113218350</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11799,6 +12284,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113218615</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11907,6 +12397,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113218804</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -12032,6 +12527,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113218869</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -12140,6 +12640,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113218935</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -12248,6 +12753,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113218991</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12356,6 +12866,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113219072</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12464,6 +12979,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113219150</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12572,6 +13092,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113219184</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12680,6 +13205,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113219211</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12788,6 +13318,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113219230</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12896,6 +13431,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113219263</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -13008,6 +13548,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113219291</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -13116,6 +13661,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113219317</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -13224,6 +13774,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113219375</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13332,6 +13887,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113219422</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13457,6 +14017,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113219436</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13582,6 +14147,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113219671</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13707,6 +14277,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113220126</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13833,6 +14408,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116996994</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13954,6 +14534,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116997051</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -14083,6 +14668,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116997238</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -14204,6 +14794,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116997630</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -14325,6 +14920,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116997732</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -14446,6 +15046,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116997917</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14567,6 +15172,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116998131</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14693,6 +15303,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116998352</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14814,6 +15429,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116998636</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14935,6 +15555,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116999020</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -15064,6 +15689,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116999396</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -15193,6 +15823,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116999846</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -15322,6 +15957,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117000062</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -15451,6 +16091,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117000334</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -15572,6 +16217,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117000422</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15698,6 +16348,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117000882</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -15815,6 +16470,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113120628</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15936,6 +16596,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113120623</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -16059,6 +16724,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84983233</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -16167,8 +16837,149 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113224764</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 47417-2023 artfynd.xlsx
+++ b/artfynd/A 47417-2023 artfynd.xlsx
@@ -926,7 +926,7 @@
         <v>136047742</v>
       </c>
       <c r="B4" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>136047769</v>
       </c>
       <c r="B9" t="n">
-        <v>92496</v>
+        <v>92497</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 47417-2023 artfynd.xlsx
+++ b/artfynd/A 47417-2023 artfynd.xlsx
@@ -926,7 +926,7 @@
         <v>136047742</v>
       </c>
       <c r="B4" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>136047769</v>
       </c>
       <c r="B9" t="n">
-        <v>92497</v>
+        <v>92498</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 47417-2023 artfynd.xlsx
+++ b/artfynd/A 47417-2023 artfynd.xlsx
@@ -926,7 +926,7 @@
         <v>136047742</v>
       </c>
       <c r="B4" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>136047769</v>
       </c>
       <c r="B9" t="n">
-        <v>92498</v>
+        <v>92499</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 47417-2023 artfynd.xlsx
+++ b/artfynd/A 47417-2023 artfynd.xlsx
@@ -926,7 +926,7 @@
         <v>136047742</v>
       </c>
       <c r="B4" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>136047769</v>
       </c>
       <c r="B9" t="n">
-        <v>92499</v>
+        <v>92505</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 47417-2023 artfynd.xlsx
+++ b/artfynd/A 47417-2023 artfynd.xlsx
@@ -926,7 +926,7 @@
         <v>136047742</v>
       </c>
       <c r="B4" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>136047769</v>
       </c>
       <c r="B9" t="n">
-        <v>92505</v>
+        <v>92506</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 47417-2023 artfynd.xlsx
+++ b/artfynd/A 47417-2023 artfynd.xlsx
@@ -926,7 +926,7 @@
         <v>136047742</v>
       </c>
       <c r="B4" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>136047769</v>
       </c>
       <c r="B9" t="n">
-        <v>92506</v>
+        <v>92512</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 47417-2023 artfynd.xlsx
+++ b/artfynd/A 47417-2023 artfynd.xlsx
@@ -926,7 +926,7 @@
         <v>136047742</v>
       </c>
       <c r="B4" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>136047769</v>
       </c>
       <c r="B9" t="n">
-        <v>92512</v>
+        <v>92519</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 47417-2023 artfynd.xlsx
+++ b/artfynd/A 47417-2023 artfynd.xlsx
@@ -926,7 +926,7 @@
         <v>136047742</v>
       </c>
       <c r="B4" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>136047769</v>
       </c>
       <c r="B9" t="n">
-        <v>92519</v>
+        <v>92520</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 47417-2023 artfynd.xlsx
+++ b/artfynd/A 47417-2023 artfynd.xlsx
@@ -926,7 +926,7 @@
         <v>136047742</v>
       </c>
       <c r="B4" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>136047769</v>
       </c>
       <c r="B9" t="n">
-        <v>92520</v>
+        <v>92533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 47417-2023 artfynd.xlsx
+++ b/artfynd/A 47417-2023 artfynd.xlsx
@@ -926,7 +926,7 @@
         <v>136047742</v>
       </c>
       <c r="B4" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>136047769</v>
       </c>
       <c r="B9" t="n">
-        <v>92533</v>
+        <v>92534</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
